--- a/SHET/TKZDZ001/tkzdzsn.xlsx
+++ b/SHET/TKZDZ001/tkzdzsn.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B6EDC0-3B1B-4189-9DED-5A776655DA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDD7264-EB3D-43AE-84F0-8A7B20794910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14040" yWindow="2505" windowWidth="12600" windowHeight="14205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -47,15 +47,6 @@
     <t>Iмакс, А</t>
   </si>
   <si>
-    <t>AN</t>
-  </si>
-  <si>
-    <t>BN</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
     <t>Название таблицы</t>
   </si>
   <si>
@@ -105,6 +96,15 @@
   </si>
   <si>
     <t>X:204, X:264</t>
+  </si>
+  <si>
+    <t>Ia СН</t>
+  </si>
+  <si>
+    <t>Ib СН</t>
+  </si>
+  <si>
+    <t>Ic СН</t>
   </si>
 </sst>
 </file>
@@ -510,13 +510,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -556,131 +556,131 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -712,18 +712,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
